--- a/output/graficos_dimensiones/comunal_d_env_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:15</t>
+    <t xml:space="preserve">2026-09-10 01:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:29</t>
+    <t xml:space="preserve">2026-09-12 22:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_los lagos.xlsx
@@ -60,18 +60,18 @@
     <t xml:space="preserve">Fresia</t>
   </si>
   <si>
+    <t xml:space="preserve">Quinchao</t>
+  </si>
+  <si>
     <t xml:space="preserve">Purranque</t>
   </si>
   <si>
+    <t xml:space="preserve">Quemchi</t>
+  </si>
+  <si>
     <t xml:space="preserve">Palena</t>
   </si>
   <si>
-    <t xml:space="preserve">Quinchao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quemchi</t>
-  </si>
-  <si>
     <t xml:space="preserve">Los Muermos</t>
   </si>
   <si>
@@ -108,15 +108,15 @@
     <t xml:space="preserve">Castro</t>
   </si>
   <si>
+    <t xml:space="preserve">Hualaihué</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dalcahue</t>
+  </si>
+  <si>
     <t xml:space="preserve">Futaleufú</t>
   </si>
   <si>
-    <t xml:space="preserve">Dalcahue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hualaihué</t>
-  </si>
-  <si>
     <t xml:space="preserve">Puerto Varas</t>
   </si>
   <si>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:41</t>
+    <t xml:space="preserve">2026-09-24 00:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -568,7 +568,7 @@
         <v>2019</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>151.8</v>
+        <v>163.52</v>
       </c>
     </row>
     <row r="3">
@@ -585,7 +585,7 @@
         <v>2019</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>146.35</v>
+        <v>159.72</v>
       </c>
     </row>
     <row r="4">
@@ -602,7 +602,7 @@
         <v>2019</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>135.41</v>
+        <v>148.25</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
         <v>2019</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>132.67</v>
+        <v>142.7</v>
       </c>
     </row>
     <row r="6">
@@ -636,7 +636,7 @@
         <v>2019</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>131.04</v>
+        <v>141.58</v>
       </c>
     </row>
     <row r="7">
@@ -653,7 +653,7 @@
         <v>2019</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>121.24</v>
+        <v>130.62</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         <v>2019</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>121.05</v>
+        <v>129.73</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         <v>2019</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>117.8</v>
+        <v>127.99</v>
       </c>
     </row>
     <row r="10">
@@ -698,13 +698,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>10303</v>
+        <v>10210</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>116.15</v>
+        <v>126.26</v>
       </c>
     </row>
     <row r="11">
@@ -715,13 +715,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>10404</v>
+        <v>10303</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>115.42</v>
+        <v>124.69</v>
       </c>
     </row>
     <row r="12">
@@ -732,13 +732,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>10210</v>
+        <v>10209</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>114.26</v>
+        <v>122.92</v>
       </c>
     </row>
     <row r="13">
@@ -749,13 +749,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>10209</v>
+        <v>10404</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>113.86</v>
+        <v>121.35</v>
       </c>
     </row>
     <row r="14">
@@ -772,7 +772,7 @@
         <v>2019</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>110.83</v>
+        <v>119.08</v>
       </c>
     </row>
     <row r="15">
@@ -789,7 +789,7 @@
         <v>2019</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>109.81</v>
+        <v>117.95</v>
       </c>
     </row>
     <row r="16">
@@ -806,7 +806,7 @@
         <v>2019</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>105.41</v>
+        <v>113.49</v>
       </c>
     </row>
     <row r="17">
@@ -823,7 +823,7 @@
         <v>2019</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>102</v>
+        <v>110.28</v>
       </c>
     </row>
     <row r="18">
@@ -840,7 +840,7 @@
         <v>2019</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>99.16</v>
+        <v>108.94</v>
       </c>
     </row>
     <row r="19">
@@ -857,7 +857,7 @@
         <v>2019</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>97.84</v>
+        <v>105.07</v>
       </c>
     </row>
     <row r="20">
@@ -874,7 +874,7 @@
         <v>2019</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>94.36</v>
+        <v>101.53</v>
       </c>
     </row>
     <row r="21">
@@ -891,7 +891,7 @@
         <v>2019</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>91.98</v>
+        <v>99.39</v>
       </c>
     </row>
     <row r="22">
@@ -908,7 +908,7 @@
         <v>2019</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>90.94</v>
+        <v>97.58</v>
       </c>
     </row>
     <row r="23">
@@ -925,7 +925,7 @@
         <v>2019</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>90.38</v>
+        <v>97.52</v>
       </c>
     </row>
     <row r="24">
@@ -942,7 +942,7 @@
         <v>2019</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>82.42</v>
+        <v>88.65</v>
       </c>
     </row>
     <row r="25">
@@ -959,7 +959,7 @@
         <v>2019</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>78.1</v>
+        <v>84.48</v>
       </c>
     </row>
     <row r="26">
@@ -970,13 +970,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>10402</v>
+        <v>10403</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>76.11</v>
+        <v>82.14</v>
       </c>
     </row>
     <row r="27">
@@ -993,7 +993,7 @@
         <v>2019</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>75.06</v>
+        <v>80.87</v>
       </c>
     </row>
     <row r="28">
@@ -1004,13 +1004,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>10403</v>
+        <v>10402</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>74.94</v>
+        <v>80.34</v>
       </c>
     </row>
     <row r="29">
@@ -1027,7 +1027,7 @@
         <v>2019</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>70.59</v>
+        <v>75.13</v>
       </c>
     </row>
     <row r="30">
@@ -1044,7 +1044,7 @@
         <v>2019</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>61.85</v>
+        <v>66.42</v>
       </c>
     </row>
     <row r="31">
@@ -1061,7 +1061,7 @@
         <v>2019</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>53.3</v>
+        <v>57.01</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:09</t>
+    <t xml:space="preserve">2026-10-02 16:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:10</t>
+    <t xml:space="preserve">2026-10-05 16:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
